--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:20:05+00:00</t>
+    <t>2026-07-28T10:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:50:36+00:00</t>
+    <t>2026-07-29T08:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,13 +79,16 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bedside swallowing screening instruments (GUSS + Yale Swallow Protocol/3-oz reused from SNOMED; EAT-10 / TOR-BSST as temporary local codes pending LOINC/SNOMED submission).</t>
+    <t>Swallowing screening instruments for the stroke care transition (GUSS + Yale Swallow Protocol/3-oz reused from SNOMED; TOR-BSST and EAT-10 as temporary local codes pending LOINC/SNOMED submission). Note that EAT-10 is a patient-reported symptom-severity tool used as a screen rather than a clinician-administered bedside swallow test, and its applicability in acute stroke is limited by aphasia and cognitive impairment.</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries no display terms, which are supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -360,14 +363,16 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -386,7 +391,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>20</v>
@@ -394,18 +399,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -418,10 +423,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -440,7 +445,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>20</v>
@@ -448,13 +453,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2"/>
     </row>
@@ -468,10 +473,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:35:16+00:00</t>
+    <t>2026-07-29T12:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries no display terms, which are supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
+    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries, for some members, the SNOMED CT International Edition English term as an unmodified display hint (not translated); the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:05:46+00:00</t>
+    <t>2026-07-31T09:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0</t>
+    <t>1.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:21:13+00:00</t>
+    <t>2026-08-13T14:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:00:50+00:00</t>
+    <t>2026-08-13T23:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries, for some members, the SNOMED CT International Edition English term as an unmodified display hint (not translated); the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
+    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries, for some members, the SNOMED CT International Edition English term as an unmodified display hint (not translated); the authoritative display is supplied at expansion time by the implementer's own terminology server. SNOMED CT® is a registered trademark of SNOMED International; those terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers must hold the applicable third-party licences.</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.2</t>
+    <t>1.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:31:20+00:00</t>
+    <t>2026-08-14T00:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.3</t>
+    <t>1.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:08:39+00:00</t>
+    <t>2026-08-14T00:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.4</t>
+    <t>1.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:48:45+00:00</t>
+    <t>2026-08-15T14:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.5</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T14:40:00+00:00</t>
+    <t>2026-08-18T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T10:55:39+00:00</t>
+    <t>2026-08-18T13:05:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.1</t>
+    <t>1.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:05:08+00:00</t>
+    <t>2026-08-18T14:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-swallow-screening-type-vs.xlsx
+++ b/ValueSet-swallow-screening-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:23:53+00:00</t>
+    <t>2026-08-19T10:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
